--- a/out/03_FAT/SNX-FAT-REG-01 Billing & Collection Monitoring Register (Rev00 DRAFT).xlsx
+++ b/out/03_FAT/SNX-FAT-REG-01 Billing & Collection Monitoring Register (Rev00 DRAFT).xlsx
@@ -1237,7 +1237,7 @@
     <row r="2">
       <c r="A2" s="70" t="inlineStr">
         <is>
-          <t>Nilai dalam IDR. Finance Staff memantau klien Gov / SOE yang lambat membayar. PPN = DPP x 12% (USULAN). Amount (IDR): Enterprise = DPP + PPN - PPh 23; Gov / SOE = DPP - PPN - PPh 22.</t>
+          <t>Dalam IDR. Finance Staff memantau klien Gov / SOE yang lambat membayar. PPN = DPP x 12% (USULAN). Amount (IDR): Enterprise = DPP + PPN - PPh 23; Gov / SOE = DPP - PPN - PPh 22 (menunggu konfirmasi FAT).</t>
         </is>
       </c>
     </row>

--- a/out/03_FAT/SNX-FAT-REG-01 Billing & Collection Monitoring Register (Rev00 DRAFT).xlsx
+++ b/out/03_FAT/SNX-FAT-REG-01 Billing & Collection Monitoring Register (Rev00 DRAFT).xlsx
@@ -1068,7 +1068,7 @@
       <c r="A24" s="63" t="n"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Days overdue = TODAY() dikurangi Due date, mengikuti pola rumus kolom Aging di AP Aging (AP memakai Invoice date).</t>
+          <t>Days overdue = TODAY() dikurangi Due date, mengikuti pola rumus kolom Aging di AP Aging (AP memakai Invoice date) (USULAN).</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       <c r="A25" s="66" t="n"/>
       <c r="B25" s="64" t="inlineStr">
         <is>
-          <t>Nilai negatif berarti belum jatuh tempo; baris yang sudah dibayar tetap terhitung.</t>
+          <t>Nilai negatif berarti belum jatuh tempo; baris yang sudah dibayar tetap terhitung (USULAN).</t>
         </is>
       </c>
     </row>
